--- a/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164415</t>
+          <t>164755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207441</t>
+          <t>208422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227942</t>
+          <t>227116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257239</t>
+          <t>257176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>399751</t>
+          <t>402813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458802</t>
+          <t>461471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265453</t>
+          <t>264472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308479</t>
+          <t>308139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>49504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78738</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320773</t>
+          <t>318104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>379824</t>
+          <t>376762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154695</t>
+          <t>153204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193037</t>
+          <t>193048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296494</t>
+          <t>296758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>325221</t>
+          <t>324874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>457490</t>
+          <t>460666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>512200</t>
+          <t>510543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173897</t>
+          <t>173886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212239</t>
+          <t>213730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46644</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>75107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226599</t>
+          <t>228256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281309</t>
+          <t>278133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161663</t>
+          <t>163056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206536</t>
+          <t>207845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137954</t>
+          <t>138263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155696</t>
+          <t>155405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309268</t>
+          <t>306527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360732</t>
+          <t>360858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335853</t>
+          <t>334544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380726</t>
+          <t>379333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349439</t>
+          <t>349313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>400903</t>
+          <t>403644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379692</t>
+          <t>381440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>446733</t>
+          <t>448707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>593451</t>
+          <t>594156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>632169</t>
+          <t>630365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>986661</t>
+          <t>977080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1068988</t>
+          <t>1070074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>791601</t>
+          <t>789627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858642</t>
+          <t>856894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80594</t>
+          <t>82398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119312</t>
+          <t>118607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>882110</t>
+          <t>881024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>964437</t>
+          <t>974018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107822</t>
+          <t>108639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144874</t>
+          <t>145524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>499954</t>
+          <t>499667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>528986</t>
+          <t>529464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>608121</t>
+          <t>611653</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>667104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205681</t>
+          <t>205031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>241916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39766</t>
+          <t>39288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68798</t>
+          <t>69085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252806</t>
+          <t>252203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>311186</t>
+          <t>307654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>974642</t>
+          <t>976797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1030174</t>
+          <t>1029210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1001521</t>
+          <t>1000714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1073478</t>
+          <t>1075250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251554</t>
+          <t>250267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273470</t>
+          <t>273581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215556</t>
+          <t>216520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271088</t>
+          <t>268933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>468680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542409</t>
+          <t>543216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1061726</t>
+          <t>1059293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1174381</t>
+          <t>1171713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2794156</t>
+          <t>2791177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2882313</t>
+          <t>2878835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3877755</t>
+          <t>3876930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4046403</t>
+          <t>4033626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2094927</t>
+          <t>2097595</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2207582</t>
+          <t>2210015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>491259</t>
+          <t>494737</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>579416</t>
+          <t>582395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2596477</t>
+          <t>2609254</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2765125</t>
+          <t>2765950</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200187</t>
+          <t>201993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>245203</t>
+          <t>244850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251265</t>
+          <t>252586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279565</t>
+          <t>278970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>459450</t>
+          <t>463423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>513983</t>
+          <t>517971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192008</t>
+          <t>192361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237024</t>
+          <t>235218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>35484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>61868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237682</t>
+          <t>233694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>292215</t>
+          <t>288242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205292</t>
+          <t>203273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249165</t>
+          <t>247621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285886</t>
+          <t>285781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311118</t>
+          <t>311418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>498332</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>556695</t>
+          <t>555733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169632</t>
+          <t>171176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>215524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200113</t>
+          <t>201075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258476</t>
+          <t>257243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>276127</t>
+          <t>273282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327158</t>
+          <t>324419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210953</t>
+          <t>209368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233569</t>
+          <t>234664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>489682</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>550379</t>
+          <t>548983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302257</t>
+          <t>304996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>353288</t>
+          <t>356133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49176</t>
+          <t>50761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339165</t>
+          <t>340561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>399862</t>
+          <t>399754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>470780</t>
+          <t>468898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>543689</t>
+          <t>539488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663919</t>
+          <t>661995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>698527</t>
+          <t>699205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1144052</t>
+          <t>1146139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1232576</t>
+          <t>1231888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615320</t>
+          <t>619521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>688229</t>
+          <t>690111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>65451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100737</t>
+          <t>102661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691090</t>
+          <t>691778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>779614</t>
+          <t>777527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183195</t>
+          <t>185450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227849</t>
+          <t>229096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>644282</t>
+          <t>641287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>680431</t>
+          <t>680393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>833101</t>
+          <t>835402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>897106</t>
+          <t>901354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>281688</t>
+          <t>280441</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>326342</t>
+          <t>324087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81091</t>
+          <t>81129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117240</t>
+          <t>120235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373952</t>
+          <t>369704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437957</t>
+          <t>435656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26871</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49647</t>
+          <t>50085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>798788</t>
+          <t>796460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>857642</t>
+          <t>855852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>828780</t>
+          <t>826124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>901714</t>
+          <t>902137</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217235</t>
+          <t>216797</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240011</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251709</t>
+          <t>253499</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310563</t>
+          <t>312891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474519</t>
+          <t>474096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547453</t>
+          <t>550109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1439668</t>
+          <t>1437884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1561711</t>
+          <t>1562531</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2917669</t>
+          <t>2919030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3011296</t>
+          <t>3009495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4379955</t>
+          <t>4379797</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4535984</t>
+          <t>4546260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1859139</t>
+          <t>1858319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1981182</t>
+          <t>1982966</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>536828</t>
+          <t>538629</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630455</t>
+          <t>629094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2432991</t>
+          <t>2422715</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2589020</t>
+          <t>2589178</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>268807</t>
+          <t>270662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>307792</t>
+          <t>310504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>288021</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314874</t>
+          <t>314528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>569207</t>
+          <t>570291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>618689</t>
+          <t>618492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120327</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159312</t>
+          <t>157457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59034</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156485</t>
+          <t>156682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205967</t>
+          <t>204883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225591</t>
+          <t>226659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264743</t>
+          <t>264437</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335047</t>
+          <t>335676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355965</t>
+          <t>356291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>569742</t>
+          <t>569436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>614225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112484</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151636</t>
+          <t>150568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133457</t>
+          <t>135275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179758</t>
+          <t>180064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265259</t>
+          <t>264963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311056</t>
+          <t>309949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142403</t>
+          <t>142161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158128</t>
+          <t>158002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415173</t>
+          <t>415522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466005</t>
+          <t>466276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209038</t>
+          <t>210145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254835</t>
+          <t>255131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220212</t>
+          <t>219941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271044</t>
+          <t>270695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>579272</t>
+          <t>577588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>647167</t>
+          <t>647473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>722460</t>
+          <t>723894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>757508</t>
+          <t>756945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1313582</t>
+          <t>1311895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1395095</t>
+          <t>1394072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498058</t>
+          <t>497752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>565953</t>
+          <t>567637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99409</t>
+          <t>97975</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571998</t>
+          <t>573021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>653511</t>
+          <t>655198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>261324</t>
+          <t>260778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312940</t>
+          <t>309816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>657633</t>
+          <t>657094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>688457</t>
+          <t>688837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>925549</t>
+          <t>923458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>990577</t>
+          <t>993833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307766</t>
+          <t>310890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>359382</t>
+          <t>359928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79657</t>
+          <t>80196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367419</t>
+          <t>364163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>432447</t>
+          <t>434538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>57025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87829</t>
+          <t>88028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>836115</t>
+          <t>833006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>889946</t>
+          <t>889872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>897588</t>
+          <t>899011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>968760</t>
+          <t>970145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197481</t>
+          <t>197282</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228419</t>
+          <t>228285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192079</t>
+          <t>192153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245910</t>
+          <t>249019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398575</t>
+          <t>397190</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469747</t>
+          <t>468324</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1731501</t>
+          <t>1730074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1852681</t>
+          <t>1850809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3033275</t>
+          <t>3041443</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3117316</t>
+          <t>3120157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4787419</t>
+          <t>4799950</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4952425</t>
+          <t>4947709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1524000</t>
+          <t>1525872</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1645180</t>
+          <t>1646607</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>409318</t>
+          <t>406477</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>493359</t>
+          <t>485191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1950890</t>
+          <t>1955606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2115896</t>
+          <t>2103365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338965</t>
+          <t>338950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381336</t>
+          <t>380685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>395936</t>
+          <t>396025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>421260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>744026</t>
+          <t>748144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>792634</t>
+          <t>795793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123876</t>
+          <t>124527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166247</t>
+          <t>166262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>50748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159351</t>
+          <t>156192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207959</t>
+          <t>203841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>291153</t>
+          <t>291292</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>335408</t>
+          <t>333847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348495</t>
+          <t>348532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>368329</t>
+          <t>367853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>651285</t>
+          <t>647732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>697309</t>
+          <t>696309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116338</t>
+          <t>117899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160593</t>
+          <t>160454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137017</t>
+          <t>138017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183041</t>
+          <t>186594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99734</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>453657</t>
+          <t>453787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141628</t>
+          <t>141368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157492</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182404</t>
+          <t>202352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>619699</t>
+          <t>620429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214607</t>
+          <t>214477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568530</t>
+          <t>558580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214910</t>
+          <t>214180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652205</t>
+          <t>632257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>664453</t>
+          <t>664665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>726619</t>
+          <t>731240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920687</t>
+          <t>920824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958394</t>
+          <t>957085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1578783</t>
+          <t>1579451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1748980</t>
+          <t>1757817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308200</t>
+          <t>303579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370366</t>
+          <t>370154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57407</t>
+          <t>57270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263932</t>
+          <t>255095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>434129</t>
+          <t>433461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>271475</t>
+          <t>269891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>318461</t>
+          <t>315728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>784781</t>
+          <t>783655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>809097</t>
+          <t>807936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1060106</t>
+          <t>1061203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1132236</t>
+          <t>1138782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156585</t>
+          <t>159318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203571</t>
+          <t>205155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>33399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56554</t>
+          <t>57680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184145</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256275</t>
+          <t>255178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89370</t>
+          <t>87267</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142100</t>
+          <t>138762</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>590994</t>
+          <t>588929</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>636590</t>
+          <t>636595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>687410</t>
+          <t>691627</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>763855</t>
+          <t>766542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98407</t>
+          <t>101745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>153240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124781</t>
+          <t>124776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170377</t>
+          <t>172442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238023</t>
+          <t>235336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>314468</t>
+          <t>310251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1579960</t>
+          <t>1468582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2239304</t>
+          <t>2249215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3231401</t>
+          <t>3229627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3335644</t>
+          <t>3328191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4616227</t>
+          <t>4676427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5577279</t>
+          <t>5565956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1136290</t>
+          <t>1126379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1795634</t>
+          <t>1907012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240854</t>
+          <t>248307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345097</t>
+          <t>346871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374813</t>
+          <t>1386136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2335865</t>
+          <t>2275665</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164755</t>
+          <t>165589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>208422</t>
+          <t>209229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227116</t>
+          <t>228870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257176</t>
+          <t>257121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402813</t>
+          <t>399203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>461471</t>
+          <t>456825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264472</t>
+          <t>263665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308139</t>
+          <t>307305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>49559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79564</t>
+          <t>77810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>318104</t>
+          <t>322750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376762</t>
+          <t>380372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153204</t>
+          <t>152047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193048</t>
+          <t>190941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296758</t>
+          <t>295980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324874</t>
+          <t>324517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>460666</t>
+          <t>458667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510543</t>
+          <t>511303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173886</t>
+          <t>175993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213730</t>
+          <t>214887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75107</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228256</t>
+          <t>227496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278133</t>
+          <t>280132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163056</t>
+          <t>163464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207845</t>
+          <t>206143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138263</t>
+          <t>137875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155405</t>
+          <t>155820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306527</t>
+          <t>305933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360858</t>
+          <t>360537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334544</t>
+          <t>336246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379333</t>
+          <t>378925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349313</t>
+          <t>349634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>403644</t>
+          <t>404238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>381440</t>
+          <t>377309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>448707</t>
+          <t>447319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>594156</t>
+          <t>596573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>630365</t>
+          <t>631157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>977080</t>
+          <t>981078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1070074</t>
+          <t>1071883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>789627</t>
+          <t>791015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>856894</t>
+          <t>861025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82398</t>
+          <t>81606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118607</t>
+          <t>116190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>881024</t>
+          <t>879215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>974018</t>
+          <t>970020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108639</t>
+          <t>107348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145524</t>
+          <t>142973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>499667</t>
+          <t>501394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>529464</t>
+          <t>530360</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>611653</t>
+          <t>613464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>667104</t>
+          <t>668293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205031</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241916</t>
+          <t>243207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69085</t>
+          <t>67358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252203</t>
+          <t>251014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307654</t>
+          <t>305843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>24754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>47846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976797</t>
+          <t>974956</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1029210</t>
+          <t>1029929</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1000714</t>
+          <t>1001938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1075250</t>
+          <t>1073328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250267</t>
+          <t>250355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273581</t>
+          <t>273447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>216520</t>
+          <t>215801</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268933</t>
+          <t>270774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>468680</t>
+          <t>470602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543216</t>
+          <t>541992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1059293</t>
+          <t>1062992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1171713</t>
+          <t>1173507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2791177</t>
+          <t>2794539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2878835</t>
+          <t>2878009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3876930</t>
+          <t>3870724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4033626</t>
+          <t>4033126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2097595</t>
+          <t>2095801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2210015</t>
+          <t>2206316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>494737</t>
+          <t>495563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582395</t>
+          <t>579033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2609254</t>
+          <t>2609754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2765950</t>
+          <t>2772156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>201993</t>
+          <t>201718</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>244850</t>
+          <t>246397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252586</t>
+          <t>254619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>278970</t>
+          <t>280045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>463423</t>
+          <t>463263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>517971</t>
+          <t>517410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192361</t>
+          <t>190814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235218</t>
+          <t>235493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35484</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61868</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233694</t>
+          <t>234255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288242</t>
+          <t>288402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203273</t>
+          <t>204299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>247621</t>
+          <t>248654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285781</t>
+          <t>287244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311418</t>
+          <t>311313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>499565</t>
+          <t>497512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>555733</t>
+          <t>553044</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>170143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215524</t>
+          <t>214498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26593</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>50767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>201075</t>
+          <t>203764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>257243</t>
+          <t>259296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>271520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>324419</t>
+          <t>324407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209368</t>
+          <t>210039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234664</t>
+          <t>233691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>488385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>548983</t>
+          <t>548883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304996</t>
+          <t>305008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356133</t>
+          <t>357895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50761</t>
+          <t>50090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>340561</t>
+          <t>340661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>399754</t>
+          <t>401159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>468898</t>
+          <t>469210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>539488</t>
+          <t>539777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>661995</t>
+          <t>662763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>699205</t>
+          <t>700751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1146139</t>
+          <t>1139314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1231888</t>
+          <t>1229867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>619521</t>
+          <t>619232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>690111</t>
+          <t>689799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65451</t>
+          <t>63905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102661</t>
+          <t>101893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691778</t>
+          <t>693799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777527</t>
+          <t>784352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185450</t>
+          <t>182758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229096</t>
+          <t>228633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>641287</t>
+          <t>641520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>680393</t>
+          <t>678897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>835402</t>
+          <t>833302</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>901354</t>
+          <t>900510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280441</t>
+          <t>280904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>324087</t>
+          <t>326779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81129</t>
+          <t>82625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>120002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369704</t>
+          <t>370548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>435656</t>
+          <t>437756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50085</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>796460</t>
+          <t>798915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>855852</t>
+          <t>856026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>826124</t>
+          <t>827022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>902137</t>
+          <t>898411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216797</t>
+          <t>217621</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240272</t>
+          <t>240358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253499</t>
+          <t>253325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312891</t>
+          <t>310436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474096</t>
+          <t>477822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>550109</t>
+          <t>549211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1437884</t>
+          <t>1434165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1562531</t>
+          <t>1554984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2919030</t>
+          <t>2922088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3009495</t>
+          <t>3006707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4379797</t>
+          <t>4380285</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4546260</t>
+          <t>4541938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1858319</t>
+          <t>1865866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1982966</t>
+          <t>1986685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>538629</t>
+          <t>541417</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>629094</t>
+          <t>626036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2422715</t>
+          <t>2427037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2589178</t>
+          <t>2588690</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>270662</t>
+          <t>268624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310504</t>
+          <t>309040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>288295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314528</t>
+          <t>315547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>570291</t>
+          <t>568250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>618492</t>
+          <t>617424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>119079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157457</t>
+          <t>159495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57691</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156682</t>
+          <t>157750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204883</t>
+          <t>206924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>226659</t>
+          <t>227036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264437</t>
+          <t>266495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335676</t>
+          <t>337258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>356291</t>
+          <t>356891</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>569436</t>
+          <t>566752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>614225</t>
+          <t>615018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>110732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150568</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135275</t>
+          <t>134482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180064</t>
+          <t>182748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>264963</t>
+          <t>265554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>309949</t>
+          <t>310130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142161</t>
+          <t>142354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158002</t>
+          <t>157669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415522</t>
+          <t>413725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466276</t>
+          <t>466053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210145</t>
+          <t>209964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255131</t>
+          <t>254540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219941</t>
+          <t>220164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270695</t>
+          <t>272492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>577588</t>
+          <t>576739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>647473</t>
+          <t>643512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>723894</t>
+          <t>723954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>756945</t>
+          <t>757323</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1311895</t>
+          <t>1311189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1394072</t>
+          <t>1396948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497752</t>
+          <t>501713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>567637</t>
+          <t>568486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>64546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97975</t>
+          <t>97915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>573021</t>
+          <t>570145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>655198</t>
+          <t>655904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>260778</t>
+          <t>259357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>309816</t>
+          <t>308995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>657094</t>
+          <t>656270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>688837</t>
+          <t>688804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>923458</t>
+          <t>924327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>993833</t>
+          <t>989597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>310890</t>
+          <t>311711</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>359928</t>
+          <t>361349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48453</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80196</t>
+          <t>81020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364163</t>
+          <t>368399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434538</t>
+          <t>433669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57025</t>
+          <t>57983</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88028</t>
+          <t>87285</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>833006</t>
+          <t>833523</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>889872</t>
+          <t>892987</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>899011</t>
+          <t>899191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>970145</t>
+          <t>969104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197282</t>
+          <t>198025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228285</t>
+          <t>227327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192153</t>
+          <t>189038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249019</t>
+          <t>248502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>397190</t>
+          <t>398231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468324</t>
+          <t>468144</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1730074</t>
+          <t>1730418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1850809</t>
+          <t>1853055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3041443</t>
+          <t>3039488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3120157</t>
+          <t>3122705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4799950</t>
+          <t>4798002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4947709</t>
+          <t>4950614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1525872</t>
+          <t>1523626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1646607</t>
+          <t>1646263</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>406477</t>
+          <t>403929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>485191</t>
+          <t>487146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1955606</t>
+          <t>1952701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2103365</t>
+          <t>2105313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>361000</t>
+          <t>392403</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338950</t>
+          <t>369266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380685</t>
+          <t>413799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>410776</t>
+          <t>449313</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>435361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421260</t>
+          <t>460485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>771776</t>
+          <t>841715</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>748144</t>
+          <t>811652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>795793</t>
+          <t>866176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>144212</t>
+          <t>158215</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124527</t>
+          <t>136819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166262</t>
+          <t>181352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50748</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>180209</t>
+          <t>196637</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156192</t>
+          <t>172176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203841</t>
+          <t>226700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>313528</t>
+          <t>335066</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>291292</t>
+          <t>313046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>333847</t>
+          <t>356674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>359996</t>
+          <t>398221</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348532</t>
+          <t>386415</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>367853</t>
+          <t>406390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>673524</t>
+          <t>733287</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>647732</t>
+          <t>706385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>696309</t>
+          <t>756698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>138218</t>
+          <t>147663</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117899</t>
+          <t>126055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160454</t>
+          <t>169683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>160802</t>
+          <t>172584</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138017</t>
+          <t>149173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186594</t>
+          <t>199486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>281530</t>
+          <t>306191</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109684</t>
+          <t>285141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>453787</t>
+          <t>327254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141368</t>
+          <t>158993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157380</t>
+          <t>176688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>476449</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202352</t>
+          <t>450598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>620429</t>
+          <t>498268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>386734</t>
+          <t>165421</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214477</t>
+          <t>144358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>558580</t>
+          <t>186471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>401397</t>
+          <t>182091</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214180</t>
+          <t>160272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632257</t>
+          <t>207942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>755615</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>664665</t>
+          <t>719293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>731240</t>
+          <t>788114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937664</t>
+          <t>816354</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920824</t>
+          <t>803762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957085</t>
+          <t>828443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1636174</t>
+          <t>1571969</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1579451</t>
+          <t>1528568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1757817</t>
+          <t>1609330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>336308</t>
+          <t>376228</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303579</t>
+          <t>343729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370154</t>
+          <t>412550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>44857</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57270</t>
+          <t>57449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>376738</t>
+          <t>421085</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255095</t>
+          <t>383724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433461</t>
+          <t>464486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>294938</t>
+          <t>355993</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>269891</t>
+          <t>331387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>315728</t>
+          <t>380813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>796658</t>
+          <t>782244</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>783655</t>
+          <t>771195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>807936</t>
+          <t>791497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1091596</t>
+          <t>1138237</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1061203</t>
+          <t>1108476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1138782</t>
+          <t>1166959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>180108</t>
+          <t>211971</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159318</t>
+          <t>187151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205155</t>
+          <t>236577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>39353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57680</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>224785</t>
+          <t>260577</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177599</t>
+          <t>231855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255178</t>
+          <t>290338</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>113863</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87267</t>
+          <t>83232</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138762</t>
+          <t>128102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>616204</t>
+          <t>683574</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>588929</t>
+          <t>656695</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>636595</t>
+          <t>709123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>730067</t>
+          <t>789217</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>691627</t>
+          <t>746972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>766542</t>
+          <t>826605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>126644</t>
+          <t>131585</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>109126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153240</t>
+          <t>153996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>145167</t>
+          <t>160707</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>135158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172442</t>
+          <t>187586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>271811</t>
+          <t>292292</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235336</t>
+          <t>254904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310251</t>
+          <t>334537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2063371</t>
+          <t>2250911</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1468582</t>
+          <t>2191844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2249215</t>
+          <t>2315368</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3272981</t>
+          <t>3299966</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3229627</t>
+          <t>3259600</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3328191</t>
+          <t>3334112</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5336351</t>
+          <t>5550875</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4676427</t>
+          <t>5463609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5565956</t>
+          <t>5624402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1312223</t>
+          <t>1191082</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1126379</t>
+          <t>1126625</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1907012</t>
+          <t>1250149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>303517</t>
+          <t>334182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>248307</t>
+          <t>300036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346871</t>
+          <t>374548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1615741</t>
+          <t>1525265</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1386136</t>
+          <t>1451738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2275665</t>
+          <t>1612531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
